--- a/etf_holdings/2026-10-20_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-20_00990A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:57</t>
+          <t>2026-10-20 21:43:41</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,27 +509,27 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0%2420</t>
+          <t>-0.62%2405</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2420</t>
+          <t>2405</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.96%406,000</t>
+          <t>2.91%406,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2.96%</t>
+          <t>2.91%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:57</t>
+          <t>2026-10-20 21:43:41</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,27 +572,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+2.75%1120</t>
+          <t>-5.8%1055</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+2.75%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.19%667,000</t>
+          <t>2.21%667,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.21%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:57</t>
+          <t>2026-10-20 21:43:42</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -635,27 +635,27 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-1.06%4205</t>
+          <t>-1.31%4150</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-1.06%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>4150</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.11%165,000</t>
+          <t>2.06%165,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.06%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -663,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:58</t>
+          <t>2026-10-20 21:43:42</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -693,40 +693,40 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.77%5125</t>
+          <t>-2.13%1605</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.77%</t>
+          <t>-2.13%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.08%134,000</t>
+          <t>2.04%420,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>134000</v>
+        <v>420000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:58</t>
+          <t>2026-10-20 21:43:42</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -756,40 +756,40 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.31%1640</t>
+          <t>-3.51%4945</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>-3.51%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>4945</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.07%420,000</t>
+          <t>2.04%134,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>420000</v>
+        <v>134000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:58</t>
+          <t>2026-10-20 21:43:42</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+0.15%3320</t>
+          <t>+0.15%3325</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -834,17 +834,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.58%158,000</t>
+          <t>1.56%158,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:58</t>
+          <t>2026-10-20 21:43:42</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -882,27 +882,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4062IBIDEN CO LTD</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-5.43%1305</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-5.43%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.42%236,200</t>
+          <t>1.42%348,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -911,11 +911,11 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>236200</v>
+        <v>348000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:59</t>
+          <t>2026-10-20 21:43:43</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -945,40 +945,40 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>6857ADVANTEST CORP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+1.85%1380</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+1.85%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.42%348,000</t>
+          <t>1.25%59,400</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>348000</v>
+        <v>59400</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:59</t>
+          <t>2026-10-20 21:43:43</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1008,40 +1008,40 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6857ADVANTEST CORP</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1.75%1970</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.27%59,400</t>
+          <t>1.15%193,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.15%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>59400</v>
+        <v>193000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:59</t>
+          <t>2026-10-20 21:43:43</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,40 +1071,40 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>6920LASERTEC CORP</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+1.26%2005</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.15%193,000</t>
+          <t>1.04%42,900</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.04%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>193000</v>
+        <v>42900</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:59</t>
+          <t>2026-10-20 21:43:43</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1134,40 +1134,40 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6920LASERTEC CORP</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-5.2%1185</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.09%42,900</t>
+          <t>0.58%156,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>0.58%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>42900</v>
+        <v>156000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:59</t>
+          <t>2026-10-20 21:43:43</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1197,232 +1197,43 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-4.18%263.5</t>
+          <t>-1.09%7745</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-4.18%</t>
+          <t>-1.09%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>263.5</t>
+          <t>7745</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.80%967,000</t>
+          <t>0.53%23,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>967000</v>
+        <v>23000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-10-20 00:29:59</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>3</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>4958臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>-1.8%547</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>-1.8%</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>0.61%364,000</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>0.61%</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>364000</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-10-20 00:29:59</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2368金像電</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>+0.4%1250</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>+0.4%</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>1250</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0.58%156,000</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>0.58%</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>156000</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-10-20 00:29:59</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>3</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>3443創意</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>+4.68%7830</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>+4.68%</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>7830</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>0.52%23,000</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>0.52%</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>23000</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>+0.02%</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>

--- a/etf_holdings/2026-10-20_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-20_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20 21:43:41</t>
+          <t>2026-10-20 21:54:32</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-20 21:43:41</t>
+          <t>2026-10-20 21:54:32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20 21:43:42</t>
+          <t>2026-10-20 21:54:34</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 21:43:42</t>
+          <t>2026-10-20 21:54:34</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20 21:43:42</t>
+          <t>2026-10-20 21:54:34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20 21:43:42</t>
+          <t>2026-10-20 21:54:34</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-20 21:43:42</t>
+          <t>2026-10-20 21:54:34</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-20 21:43:43</t>
+          <t>2026-10-20 21:54:35</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-20 21:43:43</t>
+          <t>2026-10-20 21:54:35</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-20 21:43:43</t>
+          <t>2026-10-20 21:54:35</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-20 21:43:43</t>
+          <t>2026-10-20 21:54:35</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-20 21:43:43</t>
+          <t>2026-10-20 21:54:35</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">

--- a/etf_holdings/2026-10-20_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-20_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:32</t>
+          <t>2026-10-20 22:20:22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:32</t>
+          <t>2026-10-20 22:20:22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:34</t>
+          <t>2026-10-20 22:20:24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:34</t>
+          <t>2026-10-20 22:20:24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:34</t>
+          <t>2026-10-20 22:20:24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:34</t>
+          <t>2026-10-20 22:20:24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:34</t>
+          <t>2026-10-20 22:20:24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:35</t>
+          <t>2026-10-20 22:20:25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:35</t>
+          <t>2026-10-20 22:20:25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:35</t>
+          <t>2026-10-20 22:20:25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:35</t>
+          <t>2026-10-20 22:20:25</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:35</t>
+          <t>2026-10-20 22:20:25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
